--- a/static/template2.xlsx
+++ b/static/template2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12860"/>
+    <workbookView windowWidth="30240" windowHeight="12740"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>名称</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>mouse 偷奶酪</t>
+  </si>
+  <si>
+    <t>一直小鸟在唱歌</t>
+  </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>小鸟唱歌</t>
   </si>
 </sst>
 </file>
@@ -678,12 +687,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1350,7 +1356,7 @@
     <col min="1" max="1" width="22.1057692307692" style="1" customWidth="1"/>
     <col min="2" max="2" width="38.1346153846154" customWidth="1"/>
     <col min="3" max="3" width="27.875" customWidth="1"/>
-    <col min="4" max="5" width="9.23076923076923" style="2"/>
+    <col min="4" max="5" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
@@ -1380,10 +1386,10 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>4</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>20.1</v>
       </c>
       <c r="F2" t="b">
@@ -1397,10 +1403,10 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>30.24</v>
       </c>
       <c r="F3" t="b">
@@ -1414,17 +1420,36 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>5.7</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1"/>
+    <row r="5" ht="100" customHeight="1" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="6" ht="100" customHeight="1"/>
     <row r="7" ht="100" customHeight="1"/>
     <row r="8" ht="100" customHeight="1"/>
